--- a/bolsas/bolsas_pesquisa.xlsx
+++ b/bolsas/bolsas_pesquisa.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -505,6 +505,53 @@
         </is>
       </c>
       <c r="I2" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Bolsa Teste 2026-05-02 18:37:21.994488</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Teste</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Administração</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Mestrado</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2026-12-01</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>https://google.com</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>

--- a/bolsas/bolsas_pesquisa.xlsx
+++ b/bolsas/bolsas_pesquisa.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -552,6 +552,53 @@
         </is>
       </c>
       <c r="I3" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Bolsa Teste 2026-05-02 18:55:40.243088</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Teste</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Administração</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Mestrado</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2026-12-01</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>https://google.com</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>

--- a/bolsas/bolsas_pesquisa.xlsx
+++ b/bolsas/bolsas_pesquisa.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -604,6 +604,1369 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>96 first-year PhD students named Presidential Excellence Award fellows through graduate program to advance their scholarship, research - Purdue University</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Google Scholarships</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Pesquisa</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Diversos</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Não informado</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMikwJBVV95cUxNSDlEUzNwb3I4dFUzdEpHNURTcVBtQUR2M1Y0TjVYMlNHcjZRRmMwMjZWd3QxYmx1OFZmOTYxSlhsTVV1ZnFMMEVIU0cxVkQ0MVJHc1psVkhEUDg2NVFEZTdDRXlRQTdGWEl4dUNSQ19FT2ZJZHBqcXRoUWFRa2ptVnZ6eHYzYk1jVTJ6aHpoYTdHaHpiallDY09HaDEtb3pzZUZEWlRNdV95TDRMYXd3ZWFFVkJFdTRKUUFPVk9JbFhOdlBBdVJmeUNlU1lta2pFTzRKRXU0S09oNHl0TzVBV2dkVnpjcHk5Z1g5Vjl2ZEdGNzhyaEhFWnlhbGh1RmlNODQxWFA4QmZjUXp4N0NrcHRXTQ?oc=5</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>28 Fully Funded Ph.D. Programs - U.S. News &amp; World Report</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Google Scholarships</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Pesquisa</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Diversos</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Não informado</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxPTG5HSGlQYjU1cldZZmd2WG5pVEZHZEQtRE82V0xNY2w2M19iRUQ5WVNDS2QtYTZwMVVjcVhtX1o0ekpPUkVSQWlzR2Y1R3pEeVJQVUJTeEhNYzFsSG5SampjOEZubHBvZllQSVdWaWdHdnZVYUQ5eFU4RUgzbWJZYnZtYWl0QVBKZkpvbWZlb2NscVV0ZmJRSU1lTHpDVTQ?oc=5</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Study &amp; Live in the UK: PhD Scholarship 2026 in Network Science (Fully Funded + Visa Support) at Northeastern University London - Global South Opportunities</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Google Scholarships</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Pesquisa</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Diversos</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Não informado</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMib0FVX3lxTFBEM1drRlYxOGRQX1lhMzkwclNiU1hHMHVVYzFPb1R6U0FYSXotMnhaa0hibTZoTWgzNllpaXExTHZTSDBYbE95NnpIUFA0S3hyLTZpeUhoUFkxaGs2S290RjhyY1VfenJrbzdaZWRKdw?oc=5</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Ciullo Awarded 2026 CAPCSD Ph.D. Scholarship : School of Public Health &amp; Health Sciences - UMass Amherst</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Google Scholarships</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Pesquisa</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Diversos</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Não informado</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxOdnp0UTNySjZzVnQzZy1EeW9qZU1yWXVlQW1QN0xoZHBiQ0QxT0F1WTgxcjF5aEFkdzhVSHhlblAxMVVzaVEzQWJtdUJvOTRQNXIzMmxVVFMtWjVKcG5EV01pdVFqTkQ4eXJ1QkQ1dGdmQ1B0QklIbGZ1Wk8tQ3g3Sm1XNU1fbHE0dk03UDJ1TXlHTDFPcWJB?oc=5</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>ACU partners with MacKillop Family Services on PhD scholarship to address abuse in schools - Catholic Outlook</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Google Scholarships</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Pesquisa</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Diversos</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Não informado</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxOT21jLWVBQlhibkNLaFpOVGthTklkQU1ibWJDVTVGeXNIM1VMYlozTUxaM3BoUlNOVWo2VWN3LVdVMUNxY1pja2Q4eWUtNi1UVDhuLTdtS0E0RzQ0bVZVSjhBWGJlZk9uVHNFRExKeGlLNGpuYkladk5iWk43M2hSSVBDYnlHMEl0Zjd3V0hkRjk1MlNoamZzTXV1ZzR2TEhuc0oyYzdfRGNrTzJrNnAxVEZEaG5fcFdwZmFr?oc=5</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Introducing the African Health Systems PhD Student Fund - Johns Hopkins Bloomberg School of Public Health</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Google Scholarships</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Pesquisa</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Diversos</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Não informado</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxPbm5heWNCWjBHOG5KSDdCX3M4TTA0YUQ1M2w2QXFadUI0NFNwb0FrOWp5RndRNldsMjlMdk1UN2w1RlFya2tUbkJkWlZXM2o0dWxEZTF2SzNpOXNvWGhHNWZ2VDJ1QmtuZUFKNnNOR1p1N0tNNFdHZmdIZ3FNNzI3dzdCZFR5TlBJZjJNS1lKOUlEaGc?oc=5</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>PhD candidate, Aman KC, awarded an IPCC Scholarship - Boise State University</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Google Scholarships</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Pesquisa</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Diversos</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Não informado</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxPUk1ybi1qR3pYMTU0aXdyTDJ0RGszYUtxUmJCVU9kNEljOXRLRy15TjgxVG55Tkh2czJMMmJQeERhZFdDR1drc1BuX1V3NGYxZWhKbWM5ckxVdEhZOGk1bEFYcWg5LWZyTHpNNUZieUVyUG12MWpyWkF5ZDdKdjVkVk51OEZrQW9wZEhEd253ejVwUzVUQ2RadmxB?oc=5</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>7 countries offering the highest PhD stipends - Study International</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Google Scholarships</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Pesquisa</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Diversos</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Não informado</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiaEFVX3lxTFBnaWtOcUhjVjJaRE9WRDE4SEVhaFZ4ZXJiMllMdWQwd292dlh5YkgybmhYVE1ZTlBGUm9EaTNNNG5taUEtTlVaS3Myem8xOW41QXNpQjFWTXRLQTFkZG1GX3NGd3VpYTM3?oc=5</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>NDDC Conducts CBT For 6,200 Applicants In Foreign Postgraduate Scholarship Programme - Arise News</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Google Scholarships</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Pesquisa</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Diversos</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Não informado</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxPdUh0YzdXRjViM3BjeThZSjdJYUlJS3dRRG56ZXRkaTc0Q2E1T24tRDRnUURfYmllc1hQbjlBbjd0alFERTBRWkhFQWlGSkV6d2V4eFpzY3V3ekZKTkRtd2Z1MDktaGJuUXJycHRkTHNpVExpRE9ZUjVuMUhfNlczU01NQTdUWTQ4Y1lvQnZfSV9XNVZVRlA5NV9kTllkVEhTVGFHUGY1OXk?oc=5</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Three From Johns Hopkins Earn NCAA Postgraduate Scholarships - Johns Hopkins University Athletics</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Google Scholarships</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Pesquisa</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Diversos</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Não informado</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxPX0hucWtySmJuR3VINHpQVU1UZS1ySEhTTTZ6c18zWjRWOTRHY3ROVmtQNnhmaGhoeHB6RGg4ZXJNdjk2OWtoQUZtS3NiZUFBb1pCOEJQYkNkSEdTQUNfOHlvWnV4b1JxeHdsTFdXWmN1OVB1TVlSLUJnXzlLZThvNFBoeHNkZktuVFhuSUJZNVlDWkJ6WTI1REM1STZBM0xWdmFuM2Q4eXNBNWdfTVdHcDlCTGg?oc=5</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>PhD student wins prestigious scholarship for research into disease inequity - Inside Government NZ</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Google Scholarships</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Pesquisa</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Diversos</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Não informado</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxOeXZDMHZILXdseGFFQWtCYmNtZ2hHYzBNdzlpUWI5SExBUGNQNnhrTHV1SkRDLW5yazFVdlhDZkxPVk5hdUJiTldoelJfV0h0RjUtWWFnMXliRVpmenpWbDZfck1BNjBuQWhYazVDR2hzcHVKNTZ6YUgxVEVRR0ZSQWFIZ1Fmc210T2l6QllPd2t2Z2pESTNac0ltOTktX1VOTmJyb3JabWl1cWs?oc=5</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>PhD Economics Scholarship Award Now Open - Maynooth University</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Google Scholarships</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Pesquisa</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Diversos</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Não informado</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxNUUlyZTMybGJHMlNiNWM4OWFPdW5FY2VpNlJ0XzE0QzFsQkFtVHhTVmpwMU0wcjJGdFNMVWdNcUFiZ2RFcVYyYkhUR2g5VU1EZVZDRW1PVkU5aW13ZVpEczBxRFRkMVB0MmtCVVhBbWt6bWJxMzJ5WjZ0ZFBTLWVVaUJRNGN1RWpRYkFkQnhHdw?oc=5</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>PhD student Erin Dunphy honored with Ludo Frevel Scholarship - University of Colorado Boulder</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Google Scholarships</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Pesquisa</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Diversos</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Não informado</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxPNW00cHhXaDkwM2dnS3dlNjJzeGRBajVMQVQtQmJaVDdvWXRfVzNWdnZWdENjQVNJamtZM3RyRDNpQmNzYjhtME1UZHl5eXoyb2o1VzBGNnZxRU4tVlNWbU5TbnJSNDk5SzFUaFZjNHFZOFdvVHU1YjZna2Q2Vk5xdk42eWFXdEs2T0ZOMk1qdkJGS0otNVVlVVFKVnBSV21NTzlwWmpPZ3AwUzdu?oc=5</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Introducing the EF Academic Secretariat 2026 PhD Fellowship - ethereum.org</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Google Scholarships</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Pesquisa</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Diversos</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Não informado</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiYEFVX3lxTE9HeTZIaXRvWFZpLTdycHBvR2VsczZLazlQREhGR29CQnBSUUVyclNTV214cWpZZjMtNktZZ1ZKNFhuYXlFUkt1eVZsdGMySlNtdk1ScFlpN3ZLQWxQV3R5bg?oc=5</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Study in New Zealand: University of Canterbury PhD Scholarship 2026 (Fully Funded Doctoral Opportunity) - Global South Opportunities</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Google Scholarships</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Pesquisa</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Diversos</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Não informado</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMia0FVX3lxTFAycVlXcFNXTHNubUdCNEVTa1BKbGR3S2VNM2VoY0JDTi1GVmRiSW1ZN3BEYmhuT0QxVV9scWVtTFZnMUFMS3lmdXMxMmJvNHlON2pvUzI1UWJPel9kNjVwcmNYMHY2UkUzZ1Rv?oc=5</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Civil Rights Movement will be focus of new Mississippi Archives and History research fellows - Mississippi Today</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Google Research</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Pesquisa</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Diversos</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Não informado</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNaHNyQnhfRnlTSWt0TEQ4eXo1cDR4V21Sb19RMVljcTlDcjVJcUhaeDBURlBmalZBRlVNU2ZSSFU0aDRvN3FEZmVGdk56cTdCMjhOU293WWVWaHVwU1hEc0xJRUVfOXhBOVpMNjhyS00zNlYydWtnaHg0THhIR3VqOWllc3QyeTBtdzlxa0YydnpLRXZVZTN2azlDVQ?oc=5</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Jacob Tjaden ’26 Wins Prestigious NSF Graduate Research Fellowship - Colby News</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Google Research</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Pesquisa</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Diversos</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Não informado</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxOT1JybURGMEMwSGowLUp6bFE2Wkk4NHhtVnJzVkxsblJTdG5nLUh1WWJ2WWY2SVNNcmdKbGtFS1pHUWd0RDZhNk5tNnRfVDUwdjRpN196YVBQcno0MURtLUNlQWZrLWVIeVpmSzU4MUNSRnRqV01QWktnWk56cjMzRk1vTm5Qdw?oc=5</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Drury senior awarded NSF Graduate Research Fellowship - Drury University</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Google Research</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Pesquisa</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Diversos</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Não informado</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxPUDh0eENfTUVFT1VVazRtNkcxMUtPN0R0YURtbnJYY2xVZllLQm1yVGFyNkI3Y1dNLWZ0Z2prVXcwRXBMa2FpTWUzVW5Gd21iSk9Ha2c4aFRnZV9VcmRyRnVGNm1QbnpZNUVuS0c3RktibWhpTGJNLXZwRk9yZVJRLTRBQnUxc2V3TlE?oc=5</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Minnesota fraud revelations are shocking, but not surprising: Heritage Foundation research fellow - Fox News</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Google Research</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Pesquisa</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Diversos</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Não informado</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiVkFVX3lxTE9qTHJ5WEZWR0x2WllQMjVTM0tYc1o3V0ZTM2J5REd0UXpmY25aS3FTZlJ1c3BLSkRMS0U2ZnNMT3Z3UV9kMGRWQ3hZYTlicFNQMnlvS1Jn?oc=5</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Kopera awarded research fellowship for machine learning research - Boise State University</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Google Research</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Pesquisa</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Diversos</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Não informado</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxPcGNJc2dDV2RNT29TbGhfUk1HZXpmR250bENZYWEwS0N5amRaYW1rY1BieGlFYld3cXVMeV85Y1FSQXNIZVVSYW16c1FDQ1BXMGRLZVdkbEthZ0VjOG12MHNGSk1DTnpYeWhJbXl3Y0VYTUZQZHp4UGVVTGNLMzB4TXRfQW9rYkxveHl2QV83dXpJRC0yZkZNX0V2aVE3Y2lieTdud243TEtsajNz?oc=5</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>3 Earn National Science Foundation Graduate Research Fellowships - Syracuse University Today</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Google Research</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Pesquisa</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Diversos</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Não informado</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxNYms4RVRHdDRGX3J6QTZadkJNYU9pV3hLVlBOMkUwM0J3VEktekRxa1NkbzJMSlRaR1N5Q0NteF9aeUg4b2dMOEYycUVFWWVhY2xpeUs1NFhMN3RDSEN0RWVpa1d1bTJJWC1TdUZYd0R5NTBOOFlLRTFXUlZzYTVFT28wRGc2MFNybTladEJxeVozNFdGREFFWl93NDlTZw?oc=5</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>NSF announces 2026 Graduate Research Fellowship Program award offers | NSF - U.S. National Science Foundation - National Science Foundation (.gov)</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Google Research</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Pesquisa</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Diversos</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Não informado</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxQV0dHSktBRzk2MWdRVVhJRHdNb2doenhXZmE0d3h5YVEtajVUT1lXdXlSUmZRV2V3YkVQbHhMOUt6UUZTNkNuYnJ0bXlCR1VwOTdmY2F3S08wSUJ0V0JGNXVsbWYyNmhKSFNqZUhGQ2JaNlRjcjZ5Q21xM19RcmJTQkNoa29lek0?oc=5</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Two Montana State University students win prestigious NSF Graduate Research Fellowships - Montana State University</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Google Research</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Pesquisa</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Diversos</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Não informado</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxQRkpwUzZvWHY2ajFlRWpjbnBNYlkteHdPb3dvd3E5LU8tU2hwazN2bWhZbUZTM1NMalFZNjBPUk40T29qMXNObFpsWlJsSk9yM2NOLS1LSDc3R0tRcmFidktkbTlTd1BHQS1XM0JhUXRZbFFPVzJMQ0NRM2tfS0FFMWNMSVJ0TWRwTnNmcVFsZ1VuNkNLd1F4NlhTa0ZXZmZPblZBbm1zZ200MmZ6NVlaX1JkR0FDaTZDWmJsQkMzTQ?oc=5</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Engineers receive NSF Graduate Research Fellowships - Mizzou Engineering</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Google Research</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Pesquisa</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Diversos</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Não informado</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxQX2RaWFhKTzVOZVN4YkhwUjdScThfZUFOcUYyZHhWc3NXSXdERVJYY0xuVEt5V0wzUzdaT2FhY1lRTkJCTWVINDI0dDJKVXhCU1Z5OTFzOWFhSWhVTXp3UkJfWmVVakxQMjlfbVhfbUIzR0RFWlVWT29tUFc0TWZranh1Y0o5UEZYMjZ5UzVEOEE0b2U1?oc=5</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026 National Science Foundation Graduate Research Awards &amp; Honorable Mentions - UCLA – Chemistry and Biochemistry</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Google Research</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Pesquisa</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Diversos</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Não informado</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxOVWJUX2ExR2tQWTFfY29reUxJWGxNbEozbVhfSnhlOWlWMTNuaEJPWDVQOEdPdDA1Q3l5ZHg5dFFPdnJ4VjVqMHpyMnhXdDd6cmplSkVsXy1DdVc2MkluQTFRSWIwT3lLYlZfa2cxUHJEb1pPc1BhcFZoY01iYkYtektkTzA0aGU0eE9odlQ0eWZhcUdBQnFKWWpTdEhibHhkT2FSQmxIbGlFZTZRZnE5d2psSQ?oc=5</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Public health student earns national cancer research fellowship - WashU</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Google Research</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Pesquisa</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Diversos</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Não informado</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxONDhtU1hGamRRZVBxSURNcmNyNUY2ckR6cnpjb1I5UkMzRTRNMzFGcUV4b3V1bjhJTU94Uk5LSEVUWHNQZl93eXpzSV9rZHdieTl4Qml4bWhkX3FkZXNUQjN0c05GVDNsT2ItUnpmMm9hSGFTcjdfRHJTbUJkY1hPZnNmUWg3aF80cTUwWF9JZEN3bVUxdWVCYU83TlpZQQ?oc=5</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Students Receive Prestigious National Science Foundation Graduate Research Fellowships - University of New Hampshire</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Google Research</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Pesquisa</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Diversos</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Não informado</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxOekx1aWNmSUxMdjdYbjU4LUs0bnpvREVxX0NPYkJCUU1jbmpTSWlDSGs4N1dfNVpNM0ZSeEJGMVV2cXp2elZMN3F0YklMUzBPVlV6bmQ4eVFsRWxjV3NVZ2thTkIzNEdHd0IzRHFSVURXZzl2emhEN2cxeWlHUFh2UUI2aXRQN3NwM052dXJaakh6emhLb2toNlRUb2tQcTNQYW5pSHJKNzV4ZkF6WW5nUDMxSkkyMktoSHl3?oc=5</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>UC Davis Students Secure NSF Graduate Research Fellowships for STEM Research - UC Davis College of Engineering</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Google Research</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Pesquisa</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Diversos</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Não informado</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxOcnV2UHVqMWZyQ0phb3FGMFlZVnlDa3BiTHZDNXpnSTluTDRSVUU3ZWQ5U3NncjJZZThUWFZCNWhEUEQ5WDVvSGFmeFFnTVdaaDJ3YkF1dVBqTFJveE4tNk4xdFVXazN3b0x0WU43NTgtZlNWXzVpNHdZSTRMQldSekluODBZSjVnaVEtZ2FqMTc5bmZZYmpPUTlQUmNkVmdSbUNMYk5zbzBnNVlhQ1E?oc=5</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Students, Alumnus Earn NSF Research Awards - UA News Center</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Google Research</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Pesquisa</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Diversos</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Não informado</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTFBLcUdhVW9YSEJMbi1nSTItUzJCTkV3WGdrMDlHQ196VGljSE11bU1rUmtPYnNzLXpCdzBrWjFWd2s4c0FUVkdDaU5zNzN6bWVLZ1ZvYWlNQ01UYUk3elFITjZIb19FNUU2VzBXbmtHSzJKcjFmUEFXcXdn?oc=5</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/bolsas/bolsas_pesquisa.xlsx
+++ b/bolsas/bolsas_pesquisa.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I33"/>
+  <dimension ref="A1:I39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,12 +466,14 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Bolsa Teste 2026-05-02 18:37:20.395479</t>
+          <t>Ir para o
+      Conteúdo
+      1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Teste</t>
+          <t>CNPq</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -481,22 +483,22 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Administração</t>
+          <t>Pesquisa</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Mestrado</t>
+          <t>Diversos</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>Consultar site</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://google.com</t>
+          <t>#wrapper</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -513,12 +515,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Bolsa Teste 2026-05-02 18:37:21.994488</t>
+          <t>Ir para a
+      Página Inicial
+      2</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Teste</t>
+          <t>CNPq</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -528,22 +532,22 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Administração</t>
+          <t>Pesquisa</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Mestrado</t>
+          <t>Diversos</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>Consultar site</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://google.com</t>
+          <t>/</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -560,12 +564,14 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Bolsa Teste 2026-05-02 18:55:40.243088</t>
+          <t>Ir para o menu de
+      Navegação
+      3</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Teste</t>
+          <t>CNPq</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -575,22 +581,22 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Administração</t>
+          <t>Pesquisa</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Mestrado</t>
+          <t>Diversos</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>Consultar site</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://google.com</t>
+          <t>#main-navigation</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -607,17 +613,19 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>96 first-year PhD students named Presidential Excellence Award fellows through graduate program to advance their scholarship, research - Purdue University</t>
+          <t>Ir para a
+      Busca
+      4</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Google Scholarships</t>
+          <t>CNPq</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -632,12 +640,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Não informado</t>
+          <t>Consultar site</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwJBVV95cUxNSDlEUzNwb3I4dFUzdEpHNURTcVBtQUR2M1Y0TjVYMlNHcjZRRmMwMjZWd3QxYmx1OFZmOTYxSlhsTVV1ZnFMMEVIU0cxVkQ0MVJHc1psVkhEUDg2NVFEZTdDRXlRQTdGWEl4dUNSQ19FT2ZJZHBqcXRoUWFRa2ptVnZ6eHYzYk1jVTJ6aHpoYTdHaHpiallDY09HaDEtb3pzZUZEWlRNdV95TDRMYXd3ZWFFVkJFdTRKUUFPVk9JbFhOdlBBdVJmeUNlU1lta2pFTzRKRXU0S09oNHl0TzVBV2dkVnpjcHk5Z1g5Vjl2ZEdGNzhyaEhFWnlhbGh1RmlNODQxWFA4QmZjUXp4N0NrcHRXTQ?oc=5</t>
+          <t>#govbr-busca-input</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -654,17 +662,19 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>28 Fully Funded Ph.D. Programs - U.S. News &amp; World Report</t>
+          <t>Ir para o
+      Mapa do site
+      5</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Google Scholarships</t>
+          <t>CNPq</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -679,12 +689,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Não informado</t>
+          <t>Consultar site</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxPTG5HSGlQYjU1cldZZmd2WG5pVEZHZEQtRE82V0xNY2w2M19iRUQ5WVNDS2QtYTZwMVVjcVhtX1o0ekpPUkVSQWlzR2Y1R3pEeVJQVUJTeEhNYzFsSG5SampjOEZubHBvZllQSVdWaWdHdnZVYUQ5eFU4RUgzbWJZYnZtYWl0QVBKZkpvbWZlb2NscVV0ZmJRSU1lTHpDVTQ?oc=5</t>
+          <t>#portal-footer</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -701,17 +711,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Study &amp; Live in the UK: PhD Scholarship 2026 in Network Science (Fully Funded + Visa Support) at Northeastern University London - Global South Opportunities</t>
+          <t>Abrir menu principal de navegação</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Google Scholarships</t>
+          <t>CNPq</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -726,12 +736,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Não informado</t>
+          <t>Consultar site</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMib0FVX3lxTFBEM1drRlYxOGRQX1lhMzkwclNiU1hHMHVVYzFPb1R6U0FYSXotMnhaa0hibTZoTWgzNllpaXExTHZTSDBYbE95NnpIUFA0S3hyLTZpeUhoUFkxaGs2S290RjhyY1VfenJrbzdaZWRKdw?oc=5</t>
+          <t>#</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -748,17 +758,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Ciullo Awarded 2026 CAPCSD Ph.D. Scholarship : School of Public Health &amp; Health Sciences - UMass Amherst</t>
+          <t>Conselho Nacional de Desenvolvimento Científico e Tecnológico</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Google Scholarships</t>
+          <t>CNPq</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -773,12 +783,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Não informado</t>
+          <t>Consultar site</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxOdnp0UTNySjZzVnQzZy1EeW9qZU1yWXVlQW1QN0xoZHBiQ0QxT0F1WTgxcjF5aEFkdzhVSHhlblAxMVVzaVEzQWJtdUJvOTRQNXIzMmxVVFMtWjVKcG5EV01pdVFqTkQ4eXJ1QkQ1dGdmQ1B0QklIbGZ1Wk8tQ3g3Sm1XNU1fbHE0dk03UDJ1TXlHTDFPcWJB?oc=5</t>
+          <t>https://www.gov.br/cnpq/pt-br</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -795,17 +805,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ACU partners with MacKillop Family Services on PhD scholarship to address abuse in schools - Catholic Outlook</t>
+          <t>imposto de renda</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Google Scholarships</t>
+          <t>CNPq</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -820,12 +830,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Não informado</t>
+          <t>Consultar site</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxOT21jLWVBQlhibkNLaFpOVGthTklkQU1ibWJDVTVGeXNIM1VMYlozTUxaM3BoUlNOVWo2VWN3LVdVMUNxY1pja2Q4eWUtNi1UVDhuLTdtS0E0RzQ0bVZVSjhBWGJlZk9uVHNFRExKeGlLNGpuYkladk5iWk43M2hSSVBDYnlHMEl0Zjd3V0hkRjk1MlNoamZzTXV1ZzR2TEhuc0oyYzdfRGNrTzJrNnAxVEZEaG5fcFdwZmFr?oc=5</t>
+          <t>https://www.gov.br/cnpq/pt-br/search?origem=termos&amp;SearchableText=imposto de renda</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -842,17 +852,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Introducing the African Health Systems PhD Student Fund - Johns Hopkins Bloomberg School of Public Health</t>
+          <t>assinatura</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Google Scholarships</t>
+          <t>CNPq</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -867,12 +877,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Não informado</t>
+          <t>Consultar site</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxPbm5heWNCWjBHOG5KSDdCX3M4TTA0YUQ1M2w2QXFadUI0NFNwb0FrOWp5RndRNldsMjlMdk1UN2w1RlFya2tUbkJkWlZXM2o0dWxEZTF2SzNpOXNvWGhHNWZ2VDJ1QmtuZUFKNnNOR1p1N0tNNFdHZmdIZ3FNNzI3dzdCZFR5TlBJZjJNS1lKOUlEaGc?oc=5</t>
+          <t>https://www.gov.br/cnpq/pt-br/search?origem=termos&amp;SearchableText=assinatura</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -889,17 +899,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>PhD candidate, Aman KC, awarded an IPCC Scholarship - Boise State University</t>
+          <t>Simples Nacional</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Google Scholarships</t>
+          <t>CNPq</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -914,12 +924,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Não informado</t>
+          <t>Consultar site</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxPUk1ybi1qR3pYMTU0aXdyTDJ0RGszYUtxUmJCVU9kNEljOXRLRy15TjgxVG55Tkh2czJMMmJQeERhZFdDR1drc1BuX1V3NGYxZWhKbWM5ckxVdEhZOGk1bEFYcWg5LWZyTHpNNUZieUVyUG12MWpyWkF5ZDdKdjVkVk51OEZrQW9wZEhEd253ejVwUzVUQ2RadmxB?oc=5</t>
+          <t>https://www.gov.br/cnpq/pt-br/search?origem=termos&amp;SearchableText=Simples Nacional</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -936,17 +946,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>7 countries offering the highest PhD stipends - Study International</t>
+          <t>imposto de renda</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Google Scholarships</t>
+          <t>CNPq</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -961,12 +971,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Não informado</t>
+          <t>Consultar site</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiaEFVX3lxTFBnaWtOcUhjVjJaRE9WRDE4SEVhaFZ4ZXJiMllMdWQwd292dlh5YkgybmhYVE1ZTlBGUm9EaTNNNG5taUEtTlVaS3Myem8xOW41QXNpQjFWTXRLQTFkZG1GX3NGd3VpYTM3?oc=5</t>
+          <t>https://www.gov.br/cnpq/pt-br/search?origem=termos&amp;SearchableText=imposto de renda</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -983,17 +993,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>NDDC Conducts CBT For 6,200 Applicants In Foreign Postgraduate Scholarship Programme - Arise News</t>
+          <t>assinatura</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Google Scholarships</t>
+          <t>CNPq</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1008,12 +1018,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Não informado</t>
+          <t>Consultar site</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxPdUh0YzdXRjViM3BjeThZSjdJYUlJS3dRRG56ZXRkaTc0Q2E1T24tRDRnUURfYmllc1hQbjlBbjd0alFERTBRWkhFQWlGSkV6d2V4eFpzY3V3ekZKTkRtd2Z1MDktaGJuUXJycHRkTHNpVExpRE9ZUjVuMUhfNlczU01NQTdUWTQ4Y1lvQnZfSV9XNVZVRlA5NV9kTllkVEhTVGFHUGY1OXk?oc=5</t>
+          <t>https://www.gov.br/cnpq/pt-br/search?origem=termos&amp;SearchableText=assinatura</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1030,17 +1040,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Three From Johns Hopkins Earn NCAA Postgraduate Scholarships - Johns Hopkins University Athletics</t>
+          <t>Acesso à Informação</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Google Scholarships</t>
+          <t>CNPq</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1055,12 +1065,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Não informado</t>
+          <t>Consultar site</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxPX0hucWtySmJuR3VINHpQVU1UZS1ySEhTTTZ6c18zWjRWOTRHY3ROVmtQNnhmaGhoeHB6RGg4ZXJNdjk2OWtoQUZtS3NiZUFBb1pCOEJQYkNkSEdTQUNfOHlvWnV4b1JxeHdsTFdXWmN1OVB1TVlSLUJnXzlLZThvNFBoeHNkZktuVFhuSUJZNVlDWkJ6WTI1REM1STZBM0xWdmFuM2Q4eXNBNWdfTVdHcDlCTGg?oc=5</t>
+          <t>https://www.gov.br/cnpq/pt-br/acesso-a-informacao</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1077,17 +1087,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>PhD student wins prestigious scholarship for research into disease inequity - Inside Government NZ</t>
+          <t>Institucional</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Google Scholarships</t>
+          <t>CNPq</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1102,12 +1112,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Não informado</t>
+          <t>Consultar site</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxOeXZDMHZILXdseGFFQWtCYmNtZ2hHYzBNdzlpUWI5SExBUGNQNnhrTHV1SkRDLW5yazFVdlhDZkxPVk5hdUJiTldoelJfV0h0RjUtWWFnMXliRVpmenpWbDZfck1BNjBuQWhYazVDR2hzcHVKNTZ6YUgxVEVRR0ZSQWFIZ1Fmc210T2l6QllPd2t2Z2pESTNac0ltOTktX1VOTmJyb3JabWl1cWs?oc=5</t>
+          <t>https://www.gov.br/cnpq/pt-br/acesso-a-informacao/institucional</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1124,17 +1134,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>PhD Economics Scholarship Award Now Open - Maynooth University</t>
+          <t>Apresentação</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Google Scholarships</t>
+          <t>CNPq</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1149,12 +1159,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Não informado</t>
+          <t>Consultar site</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxNUUlyZTMybGJHMlNiNWM4OWFPdW5FY2VpNlJ0XzE0QzFsQkFtVHhTVmpwMU0wcjJGdFNMVWdNcUFiZ2RFcVYyYkhUR2g5VU1EZVZDRW1PVkU5aW13ZVpEczBxRFRkMVB0MmtCVVhBbWt6bWJxMzJ5WjZ0ZFBTLWVVaUJRNGN1RWpRYkFkQnhHdw?oc=5</t>
+          <t>https://www.gov.br/cnpq/pt-br/acesso-a-informacao/institucional/institucional</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1171,17 +1181,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>PhD student Erin Dunphy honored with Ludo Frevel Scholarship - University of Colorado Boulder</t>
+          <t>Organograma</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Google Scholarships</t>
+          <t>CNPq</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1196,12 +1206,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Não informado</t>
+          <t>Consultar site</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxPNW00cHhXaDkwM2dnS3dlNjJzeGRBajVMQVQtQmJaVDdvWXRfVzNWdnZWdENjQVNJamtZM3RyRDNpQmNzYjhtME1UZHl5eXoyb2o1VzBGNnZxRU4tVlNWbU5TbnJSNDk5SzFUaFZjNHFZOFdvVHU1YjZna2Q2Vk5xdk42eWFXdEs2T0ZOMk1qdkJGS0otNVVlVVFKVnBSV21NTzlwWmpPZ3AwUzdu?oc=5</t>
+          <t>https://www.gov.br/cnpq/pt-br/acesso-a-informacao/institucional/copy_of_organograma</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1218,22 +1228,24 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Introducing the EF Academic Secretariat 2026 PhD Fellowship - ethereum.org</t>
+          <t>Ir para o
+      Conteúdo
+      1</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Google Scholarships</t>
+          <t>CAPES</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Pesquisa</t>
+          <t>Educação</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1243,12 +1255,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Não informado</t>
+          <t>Consultar site</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiYEFVX3lxTE9HeTZIaXRvWFZpLTdycHBvR2VsczZLazlQREhGR29CQnBSUUVyclNTV214cWpZZjMtNktZZ1ZKNFhuYXlFUkt1eVZsdGMySlNtdk1ScFlpN3ZLQWxQV3R5bg?oc=5</t>
+          <t>#wrapper</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1265,22 +1277,24 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Study in New Zealand: University of Canterbury PhD Scholarship 2026 (Fully Funded Doctoral Opportunity) - Global South Opportunities</t>
+          <t>Ir para a
+      Página Inicial
+      2</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Google Scholarships</t>
+          <t>CAPES</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Pesquisa</t>
+          <t>Educação</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1290,12 +1304,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Não informado</t>
+          <t>Consultar site</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMia0FVX3lxTFAycVlXcFNXTHNubUdCNEVTa1BKbGR3S2VNM2VoY0JDTi1GVmRiSW1ZN3BEYmhuT0QxVV9scWVtTFZnMUFMS3lmdXMxMmJvNHlON2pvUzI1UWJPel9kNjVwcmNYMHY2UkUzZ1Rv?oc=5</t>
+          <t>/</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1312,22 +1326,24 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Civil Rights Movement will be focus of new Mississippi Archives and History research fellows - Mississippi Today</t>
+          <t>Ir para o menu de
+      Navegação
+      3</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Google Research</t>
+          <t>CAPES</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Pesquisa</t>
+          <t>Educação</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1337,12 +1353,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Não informado</t>
+          <t>Consultar site</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNaHNyQnhfRnlTSWt0TEQ4eXo1cDR4V21Sb19RMVljcTlDcjVJcUhaeDBURlBmalZBRlVNU2ZSSFU0aDRvN3FEZmVGdk56cTdCMjhOU293WWVWaHVwU1hEc0xJRUVfOXhBOVpMNjhyS00zNlYydWtnaHg0THhIR3VqOWllc3QyeTBtdzlxa0YydnpLRXZVZTN2azlDVQ?oc=5</t>
+          <t>#main-navigation</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1359,22 +1375,24 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Jacob Tjaden ’26 Wins Prestigious NSF Graduate Research Fellowship - Colby News</t>
+          <t>Ir para a
+      Busca
+      4</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Google Research</t>
+          <t>CAPES</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Pesquisa</t>
+          <t>Educação</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1384,12 +1402,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Não informado</t>
+          <t>Consultar site</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxOT1JybURGMEMwSGowLUp6bFE2Wkk4NHhtVnJzVkxsblJTdG5nLUh1WWJ2WWY2SVNNcmdKbGtFS1pHUWd0RDZhNk5tNnRfVDUwdjRpN196YVBQcno0MURtLUNlQWZrLWVIeVpmSzU4MUNSRnRqV01QWktnWk56cjMzRk1vTm5Qdw?oc=5</t>
+          <t>#govbr-busca-input</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1406,22 +1424,24 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Drury senior awarded NSF Graduate Research Fellowship - Drury University</t>
+          <t>Ir para o
+      Mapa do site
+      5</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Google Research</t>
+          <t>CAPES</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Pesquisa</t>
+          <t>Educação</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1431,12 +1451,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Não informado</t>
+          <t>Consultar site</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxPUDh0eENfTUVFT1VVazRtNkcxMUtPN0R0YURtbnJYY2xVZllLQm1yVGFyNkI3Y1dNLWZ0Z2prVXcwRXBMa2FpTWUzVW5Gd21iSk9Ha2c4aFRnZV9VcmRyRnVGNm1QbnpZNUVuS0c3RktibWhpTGJNLXZwRk9yZVJRLTRBQnUxc2V3TlE?oc=5</t>
+          <t>#portal-footer</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1453,22 +1473,22 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Minnesota fraud revelations are shocking, but not surprising: Heritage Foundation research fellow - Fox News</t>
+          <t>Abrir menu principal de navegação</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Google Research</t>
+          <t>CAPES</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Pesquisa</t>
+          <t>Educação</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1478,12 +1498,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Não informado</t>
+          <t>Consultar site</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiVkFVX3lxTE9qTHJ5WEZWR0x2WllQMjVTM0tYc1o3V0ZTM2J5REd0UXpmY25aS3FTZlJ1c3BLSkRMS0U2ZnNMT3Z3UV9kMGRWQ3hZYTlicFNQMnlvS1Jn?oc=5</t>
+          <t>#</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1500,22 +1520,22 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Kopera awarded research fellowship for machine learning research - Boise State University</t>
+          <t>imposto de renda</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Google Research</t>
+          <t>CAPES</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Pesquisa</t>
+          <t>Educação</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1525,12 +1545,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Não informado</t>
+          <t>Consultar site</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxPcGNJc2dDV2RNT29TbGhfUk1HZXpmR250bENZYWEwS0N5amRaYW1rY1BieGlFYld3cXVMeV85Y1FSQXNIZVVSYW16c1FDQ1BXMGRLZVdkbEthZ0VjOG12MHNGSk1DTnpYeWhJbXl3Y0VYTUZQZHp4UGVVTGNLMzB4TXRfQW9rYkxveHl2QV83dXpJRC0yZkZNX0V2aVE3Y2lieTdud243TEtsajNz?oc=5</t>
+          <t>https://www.gov.br/capes/pt-br/search?origem=termos&amp;SearchableText=imposto de renda</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1547,22 +1567,22 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>3 Earn National Science Foundation Graduate Research Fellowships - Syracuse University Today</t>
+          <t>assinatura</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Google Research</t>
+          <t>CAPES</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Pesquisa</t>
+          <t>Educação</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1572,12 +1592,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Não informado</t>
+          <t>Consultar site</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxNYms4RVRHdDRGX3J6QTZadkJNYU9pV3hLVlBOMkUwM0J3VEktekRxa1NkbzJMSlRaR1N5Q0NteF9aeUg4b2dMOEYycUVFWWVhY2xpeUs1NFhMN3RDSEN0RWVpa1d1bTJJWC1TdUZYd0R5NTBOOFlLRTFXUlZzYTVFT28wRGc2MFNybTladEJxeVozNFdGREFFWl93NDlTZw?oc=5</t>
+          <t>https://www.gov.br/capes/pt-br/search?origem=termos&amp;SearchableText=assinatura</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1594,22 +1614,22 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>NSF announces 2026 Graduate Research Fellowship Program award offers | NSF - U.S. National Science Foundation - National Science Foundation (.gov)</t>
+          <t>Simples Nacional</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Google Research</t>
+          <t>CAPES</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Pesquisa</t>
+          <t>Educação</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1619,12 +1639,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Não informado</t>
+          <t>Consultar site</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxQV0dHSktBRzk2MWdRVVhJRHdNb2doenhXZmE0d3h5YVEtajVUT1lXdXlSUmZRV2V3YkVQbHhMOUt6UUZTNkNuYnJ0bXlCR1VwOTdmY2F3S08wSUJ0V0JGNXVsbWYyNmhKSFNqZUhGQ2JaNlRjcjZ5Q21xM19RcmJTQkNoa29lek0?oc=5</t>
+          <t>https://www.gov.br/capes/pt-br/search?origem=termos&amp;SearchableText=Simples Nacional</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1641,22 +1661,22 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Two Montana State University students win prestigious NSF Graduate Research Fellowships - Montana State University</t>
+          <t>imposto de renda</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Google Research</t>
+          <t>CAPES</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Pesquisa</t>
+          <t>Educação</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1666,12 +1686,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Não informado</t>
+          <t>Consultar site</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxQRkpwUzZvWHY2ajFlRWpjbnBNYlkteHdPb3dvd3E5LU8tU2hwazN2bWhZbUZTM1NMalFZNjBPUk40T29qMXNObFpsWlJsSk9yM2NOLS1LSDc3R0tRcmFidktkbTlTd1BHQS1XM0JhUXRZbFFPVzJMQ0NRM2tfS0FFMWNMSVJ0TWRwTnNmcVFsZ1VuNkNLd1F4NlhTa0ZXZmZPblZBbm1zZ200MmZ6NVlaX1JkR0FDaTZDWmJsQkMzTQ?oc=5</t>
+          <t>https://www.gov.br/capes/pt-br/search?origem=termos&amp;SearchableText=imposto de renda</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1688,22 +1708,22 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Engineers receive NSF Graduate Research Fellowships - Mizzou Engineering</t>
+          <t>assinatura</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Google Research</t>
+          <t>CAPES</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Pesquisa</t>
+          <t>Educação</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1713,12 +1733,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Não informado</t>
+          <t>Consultar site</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxQX2RaWFhKTzVOZVN4YkhwUjdScThfZUFOcUYyZHhWc3NXSXdERVJYY0xuVEt5V0wzUzdaT2FhY1lRTkJCTWVINDI0dDJKVXhCU1Z5OTFzOWFhSWhVTXp3UkJfWmVVakxQMjlfbVhfbUIzR0RFWlVWT29tUFc0TWZranh1Y0o5UEZYMjZ5UzVEOEE0b2U1?oc=5</t>
+          <t>https://www.gov.br/capes/pt-br/search?origem=termos&amp;SearchableText=assinatura</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1735,22 +1755,22 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026 National Science Foundation Graduate Research Awards &amp; Honorable Mentions - UCLA – Chemistry and Biochemistry</t>
+          <t>Editais e resultados CAPES</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Google Research</t>
+          <t>CAPES</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Pesquisa</t>
+          <t>Educação</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1760,12 +1780,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Não informado</t>
+          <t>Consultar site</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxOVWJUX2ExR2tQWTFfY29reUxJWGxNbEozbVhfSnhlOWlWMTNuaEJPWDVQOEdPdDA1Q3l5ZHg5dFFPdnJ4VjVqMHpyMnhXdDd6cmplSkVsXy1DdVc2MkluQTFRSWIwT3lLYlZfa2cxUHJEb1pPc1BhcFZoY01iYkYtektkTzA0aGU0eE9odlQ0eWZhcUdBQnFKWWpTdEhibHhkT2FSQmxIbGlFZTZRZnE5d2psSQ?oc=5</t>
+          <t>https://www.gov.br/capes/pt-br/assuntos/editais-e-resultados-capes</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1782,22 +1802,22 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Public health student earns national cancer research fellowship - WashU</t>
+          <t>Resultados 2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Google Research</t>
+          <t>CAPES</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Pesquisa</t>
+          <t>Educação</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1807,12 +1827,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Não informado</t>
+          <t>Consultar site</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxONDhtU1hGamRRZVBxSURNcmNyNUY2ckR6cnpjb1I5UkMzRTRNMzFGcUV4b3V1bjhJTU94Uk5LSEVUWHNQZl93eXpzSV9rZHdieTl4Qml4bWhkX3FkZXNUQjN0c05GVDNsT2ItUnpmMm9hSGFTcjdfRHJTbUJkY1hPZnNmUWg3aF80cTUwWF9JZEN3bVUxdWVCYU83TlpZQQ?oc=5</t>
+          <t>https://www.gov.br/capes/pt-br/assuntos/editais-e-resultados-capes/resultados-2026</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1829,22 +1849,22 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Students Receive Prestigious National Science Foundation Graduate Research Fellowships - University of New Hampshire</t>
+          <t>Resultados 2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Google Research</t>
+          <t>CAPES</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Pesquisa</t>
+          <t>Educação</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1854,12 +1874,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Não informado</t>
+          <t>Consultar site</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxOekx1aWNmSUxMdjdYbjU4LUs0bnpvREVxX0NPYkJCUU1jbmpTSWlDSGs4N1dfNVpNM0ZSeEJGMVV2cXp2elZMN3F0YklMUzBPVlV6bmQ4eVFsRWxjV3NVZ2thTkIzNEdHd0IzRHFSVURXZzl2emhEN2cxeWlHUFh2UUI2aXRQN3NwM052dXJaakh6emhLb2toNlRUb2tQcTNQYW5pSHJKNzV4ZkF6WW5nUDMxSkkyMktoSHl3?oc=5</t>
+          <t>https://www.gov.br/capes/pt-br/assuntos/editais-e-resultados-capes/resultados-2025</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1876,12 +1896,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>UC Davis Students Secure NSF Graduate Research Fellowships for STEM Research - UC Davis College of Engineering</t>
+          <t>Posts recentes</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Google Research</t>
+          <t>Fulbright</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1891,7 +1911,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Pesquisa</t>
+          <t>Diversos</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1901,12 +1921,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Não informado</t>
+          <t>Consultar site</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxOcnV2UHVqMWZyQ0phb3FGMFlZVnlDa3BiTHZDNXpnSTluTDRSVUU3ZWQ5U3NncjJZZThUWFZCNWhEUEQ5WDVvSGFmeFFnTVdaaDJ3YkF1dVBqTFJveE4tNk4xdFVXazN3b0x0WU43NTgtZlNWXzVpNHdZSTRMQldSekluODBZSjVnaVEtZ2FqMTc5bmZZYmpPUTlQUmNkVmdSbUNMYk5zbzBnNVlhQ1E?oc=5</t>
+          <t>https://fulbright.org.br/bolsas/</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1923,12 +1943,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Students, Alumnus Earn NSF Research Awards - UA News Center</t>
+          <t>Most Used Categories</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Google Research</t>
+          <t>Fulbright</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1938,30 +1958,312 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
+          <t>Diversos</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Diversos</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Consultar site</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://fulbright.org.br/bolsas/</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Arquivos</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Fulbright</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Diversos</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Diversos</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Consultar site</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://fulbright.org.br/bolsas/</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>other selected funding organisations</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>DAAD</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Alemanha</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Diversos</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Diversos</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Consultar site</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.daad.de/en/study-and-research-in-germany/scholarships/scholarship-database/information-on-other-funding-organisations/</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>More Information</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>DAAD</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Alemanha</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Diversos</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Diversos</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Consultar site</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.daad.de/deutschland/stipendium/hinweise/en/27334-frequently-asked-questions/</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>« Reset options &amp; show all</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>DAAD</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Alemanha</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Diversos</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Diversos</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Consultar site</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>#reset-form</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>important scholarship information</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>DAAD</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Alemanha</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Diversos</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Diversos</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Consultar site</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.daad.de/en/study-and-research-in-germany/scholarships/important-information-for-scholarship-applicants/</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Chamadas Horizon Europe (Portal Oficial)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Horizon Europe</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
           <t>Pesquisa</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>Diversos</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Não informado</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTFBLcUdhVW9YSEJMbi1nSTItUzJCTkV3WGdrMDlHQ196VGljSE11bU1rUmtPYnNzLXpCdzBrWjFWd2s4c0FUVkdDaU5zNzN6bWVLZ1ZvYWlNQ01UYUk3elFITjZIb19FNUU2VzBXbmtHSzJKcjFmUEFXcXdn?oc=5</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Doutorado/Pós-doc</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Variável</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>

--- a/bolsas/bolsas_pesquisa.xlsx
+++ b/bolsas/bolsas_pesquisa.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bolsas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I39"/>
+  <dimension ref="A1:I52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,9 +466,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Ir para o
-      Conteúdo
-      1</t>
+          <t>Bolsas e Auxílios</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,17 +486,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>Pesquisa / Geral</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Consultar site</t>
+          <t>Consultar edital</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>#wrapper</t>
+          <t>https://www.gov.br/cnpq/pt-br/acesso-a-informacao/bolsas-e-auxilios</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -515,9 +513,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Ir para a
-      Página Inicial
-      2</t>
+          <t>Bolsas no País e no Exterior</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -537,17 +533,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>Pesquisa / Geral</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Consultar site</t>
+          <t>Consultar edital</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>https://www.gov.br/cnpq/pt-br/acesso-a-informacao/bolsas-e-auxilios/copy_of_modalidades</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -564,9 +560,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Ir para o menu de
-      Navegação
-      3</t>
+          <t>Auxílios</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -586,17 +580,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>Pesquisa / Geral</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Consultar site</t>
+          <t>Consultar edital</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>#main-navigation</t>
+          <t>https://www.gov.br/cnpq/pt-br/acesso-a-informacao/bolsas-e-auxilios/auxilios-1</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -613,9 +607,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Ir para a
-      Busca
-      4</t>
+          <t>Cartão Pesquisa</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -635,17 +627,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>Pesquisa / Geral</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Consultar site</t>
+          <t>Consultar edital</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>#govbr-busca-input</t>
+          <t>https://www.gov.br/cnpq/pt-br/acesso-a-informacao/bolsas-e-auxilios/auxilios-cartao-pesquisa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -662,9 +654,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Ir para o
-      Mapa do site
-      5</t>
+          <t>Pesquisa em Pauta</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -684,17 +674,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>Pesquisa / Geral</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Consultar site</t>
+          <t>Consultar edital</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>#portal-footer</t>
+          <t>https://www.gov.br/cnpq/pt-br/assuntos/noticias/pesquisa-do-dia</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -711,7 +701,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Abrir menu principal de navegação</t>
+          <t>Relatório de Pesquisa</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -731,17 +721,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>Pesquisa / Geral</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Consultar site</t>
+          <t>Consultar edital</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>https://www.gov.br/cnpq/pt-br/assuntos/popularizacao-da-ciencia/relatorios-de-pesquisa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -758,7 +748,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Conselho Nacional de Desenvolvimento Científico e Tecnológico</t>
+          <t>Sisgen Pesquisa</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -778,17 +768,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>Pesquisa / Geral</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Consultar site</t>
+          <t>Consultar edital</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.gov.br/cnpq/pt-br</t>
+          <t>https://sisgen-pesquisa.cnpq.br</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -805,7 +795,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>imposto de renda</t>
+          <t>Serviços para Imigrantes</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -825,17 +815,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>Pesquisa / Geral</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Consultar site</t>
+          <t>Consultar edital</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.gov.br/cnpq/pt-br/search?origem=termos&amp;SearchableText=imposto de renda</t>
+          <t>https://www.gov.br/pt-br/temas/servicos-para-imigrantes</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -852,7 +842,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>assinatura</t>
+          <t>Educação e Pesquisa</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -872,17 +862,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>Pesquisa / Geral</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Consultar site</t>
+          <t>Consultar edital</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.gov.br/cnpq/pt-br/search?origem=termos&amp;SearchableText=assinatura</t>
+          <t>https://www.gov.br/pt-br/noticias/educacao-e-pesquisa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -899,7 +889,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Simples Nacional</t>
+          <t>Bolsas no País e no Exterior</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -919,17 +909,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>Pesquisa / Geral</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Consultar site</t>
+          <t>Consultar edital</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.gov.br/cnpq/pt-br/search?origem=termos&amp;SearchableText=Simples Nacional</t>
+          <t>https://www.gov.br/cnpq/pt-br/acesso-a-informacao/bolsas-e-auxilios/copy_of_modalidades</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -946,7 +936,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>imposto de renda</t>
+          <t>Auxílios</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -966,17 +956,17 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>Pesquisa / Geral</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Consultar site</t>
+          <t>Consultar edital</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.gov.br/cnpq/pt-br/search?origem=termos&amp;SearchableText=imposto de renda</t>
+          <t>https://www.gov.br/cnpq/pt-br/acesso-a-informacao/bolsas-e-auxilios/auxilios-1</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -993,7 +983,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>assinatura</t>
+          <t>Cartão Pesquisa</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1013,17 +1003,17 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>Pesquisa / Geral</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Consultar site</t>
+          <t>Consultar edital</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.gov.br/cnpq/pt-br/search?origem=termos&amp;SearchableText=assinatura</t>
+          <t>https://www.gov.br/cnpq/pt-br/acesso-a-informacao/bolsas-e-auxilios/auxilios-cartao-pesquisa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1040,7 +1030,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Acesso à Informação</t>
+          <t>Painel de Bolsas e Projetos VigentesFornece uma fotografia do fomento atual do CNPq. Além do número total de projetos ou de bolsas vigentes em cada uma das 13 dimensões disponibilizadas.</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1060,17 +1050,17 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>Pesquisa / Geral</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Consultar site</t>
+          <t>Consultar edital</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.gov.br/cnpq/pt-br/acesso-a-informacao</t>
+          <t>https://www.gov.br/cnpq/pt-br/acesso-a-informacao/bolsas-e-auxilios/mapa-de-fomento-em-ciencia-tecnologia-e-inovacao</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1087,7 +1077,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Institucional</t>
+          <t>Bolsas e Auxílios</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1107,17 +1097,17 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>Pesquisa / Geral</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Consultar site</t>
+          <t>Consultar edital</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.gov.br/cnpq/pt-br/acesso-a-informacao/institucional</t>
+          <t>https://www.gov.br/cnpq/pt-br/acesso-a-informacao/bolsas-e-auxilios</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1134,7 +1124,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Apresentação</t>
+          <t>Bolsas no País e no Exterior</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1154,17 +1144,17 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>Pesquisa / Geral</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Consultar site</t>
+          <t>Consultar edital</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.gov.br/cnpq/pt-br/acesso-a-informacao/institucional/institucional</t>
+          <t>https://www.gov.br/cnpq/pt-br/acesso-a-informacao/bolsas-e-auxilios/copy_of_modalidades</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1181,7 +1171,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Organograma</t>
+          <t>Auxílios</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1201,17 +1191,17 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>Pesquisa / Geral</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Consultar site</t>
+          <t>Consultar edital</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.gov.br/cnpq/pt-br/acesso-a-informacao/institucional/copy_of_organograma</t>
+          <t>https://www.gov.br/cnpq/pt-br/acesso-a-informacao/bolsas-e-auxilios/auxilios-1</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1228,14 +1218,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Ir para o
-      Conteúdo
-      1</t>
+          <t>Cartão Pesquisa</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CAPES</t>
+          <t>CNPq</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1245,22 +1233,22 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Educação</t>
+          <t>Pesquisa</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>Pesquisa / Geral</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Consultar site</t>
+          <t>Consultar edital</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>#wrapper</t>
+          <t>https://www.gov.br/cnpq/pt-br/acesso-a-informacao/bolsas-e-auxilios/auxilios-cartao-pesquisa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1277,14 +1265,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Ir para a
-      Página Inicial
-      2</t>
+          <t>Pesquisa em Pauta</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>CAPES</t>
+          <t>CNPq</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1294,22 +1280,22 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Educação</t>
+          <t>Pesquisa</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>Pesquisa / Geral</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Consultar site</t>
+          <t>Consultar edital</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>https://www.gov.br/cnpq/pt-br/assuntos/noticias/pesquisa-do-dia</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1326,14 +1312,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Ir para o menu de
-      Navegação
-      3</t>
+          <t>Relatório de Pesquisa</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>CAPES</t>
+          <t>CNPq</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1343,22 +1327,22 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Educação</t>
+          <t>Pesquisa</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>Pesquisa / Geral</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Consultar site</t>
+          <t>Consultar edital</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>#main-navigation</t>
+          <t>https://www.gov.br/cnpq/pt-br/assuntos/popularizacao-da-ciencia/relatorios-de-pesquisa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1375,14 +1359,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Ir para a
-      Busca
-      4</t>
+          <t>Sisgen Pesquisa</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>CAPES</t>
+          <t>CNPq</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1392,22 +1374,22 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Educação</t>
+          <t>Pesquisa</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>Pesquisa / Geral</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Consultar site</t>
+          <t>Consultar edital</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>#govbr-busca-input</t>
+          <t>https://sisgen-pesquisa.cnpq.br</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1424,9 +1406,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Ir para o
-      Mapa do site
-      5</t>
+          <t>Prêmio CAPES/Fundação Grupo Volkswagen de Excelência em Pesquisa em Mobilidade Urbana Sustentável</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1441,22 +1421,22 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Educação</t>
+          <t>Pesquisa</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>Pesquisa / Geral</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Consultar site</t>
+          <t>Consultar edital</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>#portal-footer</t>
+          <t>https://www.gov.br/capes/pt-br/assuntos/premios/premio-capes-fundacao-grupo-volkswagen-de-excelencia-em-pesquisa-em-mobilidade-urbana-sustentavel</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1473,7 +1453,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Abrir menu principal de navegação</t>
+          <t>Prêmio CAPES - Natura Campus de Excelência em Pesquisa</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1488,22 +1468,22 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Educação</t>
+          <t>Pesquisa</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>Pesquisa / Geral</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Consultar site</t>
+          <t>Consultar edital</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>https://www.gov.br/capes/pt-br/assuntos/premios/premio-capes-natura</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1520,7 +1500,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>imposto de renda</t>
+          <t>Seminário Estruturas em Aço, Ensino e Pesquisa Científica e Tecnológica.</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1535,22 +1515,22 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Educação</t>
+          <t>Pesquisa</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>Pesquisa / Geral</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Consultar site</t>
+          <t>Consultar edital</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/search?origem=termos&amp;SearchableText=imposto de renda</t>
+          <t>https://www.gov.br/capes/pt-br/assuntos/eventos/seminario-estruturas-em-aco-ensino-e-pesquisa-cientifica-e-tecnologica</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1567,7 +1547,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>assinatura</t>
+          <t>Bolsas e Estudantes</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1582,22 +1562,22 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Educação</t>
+          <t>Pesquisa</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>Pesquisa / Geral</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Consultar site</t>
+          <t>Consultar edital</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/search?origem=termos&amp;SearchableText=assinatura</t>
+          <t>https://www.gov.br/capes/pt-br/acesso-a-informacao/acoes-e-programas/bolsas</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1614,7 +1594,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Simples Nacional</t>
+          <t>Edital seleção</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1629,22 +1609,22 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Educação</t>
+          <t>Pesquisa</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>Pesquisa / Geral</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Consultar site</t>
+          <t>Consultar edital</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/search?origem=termos&amp;SearchableText=Simples Nacional</t>
+          <t>https://www.gov.br/capes/pt-br/acesso-a-informacao/servidores/edital-selecao</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1661,7 +1641,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>imposto de renda</t>
+          <t>Bolsas e Auxílios Internacionais</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1676,22 +1656,22 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Educação</t>
+          <t>Pesquisa</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>Pesquisa / Geral</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Consultar site</t>
+          <t>Consultar edital</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/search?origem=termos&amp;SearchableText=imposto de renda</t>
+          <t>https://www.gov.br/capes/pt-br/acesso-a-informacao/perguntas-frequentes/bolsas-e-auxilios-internacionais</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1708,7 +1688,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>assinatura</t>
+          <t>Programas e Bolsas no País</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1723,22 +1703,22 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Educação</t>
+          <t>Pesquisa</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>Pesquisa / Geral</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Consultar site</t>
+          <t>Consultar edital</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/search?origem=termos&amp;SearchableText=assinatura</t>
+          <t>https://www.gov.br/capes/pt-br/acesso-a-informacao/perguntas-frequentes/programas-e-bolsas-no-pais</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1755,7 +1735,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Editais e resultados CAPES</t>
+          <t>Pesquisa Pública</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1770,22 +1750,22 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Educação</t>
+          <t>Pesquisa</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>Pesquisa / Geral</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Consultar site</t>
+          <t>Consultar edital</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/assuntos/editais-e-resultados-capes</t>
+          <t>https://sei.capes.gov.br/sei/modulos/pesquisa/md_pesq_processo_pesquisar.php?acao_externa=protocolo_pesquisar&amp;acao_origem_externa=protocolo_pesquisar&amp;id_orgao_acesso_externo=1</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1802,7 +1782,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Resultados 2026</t>
+          <t>Auxílio Financeiro a Projeto Educacional ou de Pesquisa e Pós-Graduação - AUXPE</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1817,22 +1797,22 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Educação</t>
+          <t>Pesquisa</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>Pós-doc</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Consultar site</t>
+          <t>Consultar edital</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/assuntos/editais-e-resultados-capes/resultados-2026</t>
+          <t>https://www.gov.br/capes/pt-br/acesso-a-informacao/prestacao-de-contas-e-cobranca-administrativa/auxilio-financeiro-a-projeto-educacional-ou-de-pesquisa-e-pos-graduacao-auxpe</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1849,7 +1829,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Resultados 2025</t>
+          <t>Manual Cartão Pesquisador</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1864,22 +1844,22 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Educação</t>
+          <t>Pesquisa</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>Pesquisa / Geral</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Consultar site</t>
+          <t>Consultar edital</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/assuntos/editais-e-resultados-capes/resultados-2025</t>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/documentos/09042024_manual-cartao-pesquisador-capes-2024-v04.pdf</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1896,37 +1876,37 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Posts recentes</t>
+          <t>Termo Uso e Politica de Privacidade App Pesquisador</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Fulbright</t>
+          <t>CAPES</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>Pesquisa</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>Pesquisa / Geral</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Consultar site</t>
+          <t>Consultar edital</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://fulbright.org.br/bolsas/</t>
+          <t>https://www.gov.br/capes/pt-br/acesso-a-informacao/privacidade-e-protecao-de-dados-pessoais/termo-uso-e-politica-de-privacidade-app-pesquisador</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1943,37 +1923,37 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Most Used Categories</t>
+          <t>Serviços para Imigrantes</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Fulbright</t>
+          <t>CAPES</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>Pesquisa</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>Pesquisa / Geral</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Consultar site</t>
+          <t>Consultar edital</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://fulbright.org.br/bolsas/</t>
+          <t>https://www.gov.br/pt-br/temas/servicos-para-imigrantes</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1990,37 +1970,37 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Arquivos</t>
+          <t>Educação e Pesquisa</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Fulbright</t>
+          <t>CAPES</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>Pesquisa</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>Pesquisa / Geral</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Consultar site</t>
+          <t>Consultar edital</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://fulbright.org.br/bolsas/</t>
+          <t>https://www.gov.br/pt-br/noticias/educacao-e-pesquisa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2037,37 +2017,37 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>other selected funding organisations</t>
+          <t>Bolsas e Auxílios Internacionais</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>DAAD</t>
+          <t>CAPES</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Alemanha</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>Pesquisa</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>Pesquisa / Geral</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Consultar site</t>
+          <t>Consultar edital</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.daad.de/en/study-and-research-in-germany/scholarships/scholarship-database/information-on-other-funding-organisations/</t>
+          <t>https://www.gov.br/capes/pt-br/acesso-a-informacao/acoes-e-programas/bolsas/bolsas-e-auxilios-internacionais/</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2084,37 +2064,37 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>More Information</t>
+          <t>Valores de Bolsas</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>DAAD</t>
+          <t>CAPES</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Alemanha</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>Pesquisa</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>Pesquisa / Geral</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Consultar site</t>
+          <t>Consultar edital</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.daad.de/deutschland/stipendium/hinweise/en/27334-frequently-asked-questions/</t>
+          <t>https://www.gov.br/capes/pt-br/acesso-a-informacao/acoes-e-programas/bolsas/prestacao-de-contas/valores-de-bolsas</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2131,37 +2111,37 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>« Reset options &amp; show all</t>
+          <t>Prêmio CAPES/Fundação Grupo Volkswagen de Excelência em Pesquisa em Mobilidade Urbana Sustentável</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>DAAD</t>
+          <t>CAPES</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Alemanha</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>Pesquisa</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>Pesquisa / Geral</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Consultar site</t>
+          <t>Consultar edital</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>#reset-form</t>
+          <t>https://www.gov.br/capes/pt-br/assuntos/premios/premio-capes-fundacao-grupo-volkswagen-de-excelencia-em-pesquisa-em-mobilidade-urbana-sustentavel</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2178,37 +2158,37 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>important scholarship information</t>
+          <t>Prêmio CAPES - Natura Campus de Excelência em Pesquisa</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>DAAD</t>
+          <t>CAPES</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Alemanha</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>Pesquisa</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Diversos</t>
+          <t>Pesquisa / Geral</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Consultar site</t>
+          <t>Consultar edital</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.daad.de/en/study-and-research-in-germany/scholarships/important-information-for-scholarship-applicants/</t>
+          <t>https://www.gov.br/capes/pt-br/assuntos/premios/premio-capes-natura</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2225,45 +2205,656 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Chamadas Horizon Europe (Portal Oficial)</t>
+          <t>Seminário Estruturas em Aço, Ensino e Pesquisa Científica e Tecnológica.</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
+          <t>CAPES</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Pesquisa</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Pesquisa / Geral</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.gov.br/capes/pt-br/assuntos/eventos/seminario-estruturas-em-aco-ensino-e-pesquisa-cientifica-e-tecnologica</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Bolsas e Estudantes</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>CAPES</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Pesquisa</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Pesquisa / Geral</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.gov.br/capes/pt-br/acesso-a-informacao/acoes-e-programas/bolsas</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Edital seleção</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>CAPES</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Pesquisa</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Pesquisa / Geral</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.gov.br/capes/pt-br/acesso-a-informacao/servidores/edital-selecao</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Bolsas e Auxílios Internacionais</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>CAPES</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Pesquisa</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Pesquisa / Geral</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.gov.br/capes/pt-br/acesso-a-informacao/perguntas-frequentes/bolsas-e-auxilios-internacionais</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Programas e Bolsas no País</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>CAPES</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Pesquisa</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Pesquisa / Geral</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://www.gov.br/capes/pt-br/acesso-a-informacao/perguntas-frequentes/programas-e-bolsas-no-pais</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Pesquisa Pública</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>CAPES</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Pesquisa</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Pesquisa / Geral</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://sei.capes.gov.br/sei/modulos/pesquisa/md_pesq_processo_pesquisar.php?acao_externa=protocolo_pesquisar&amp;acao_origem_externa=protocolo_pesquisar&amp;id_orgao_acesso_externo=1</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Auxílio Financeiro a Projeto Educacional ou de Pesquisa e Pós-Graduação - AUXPE</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>CAPES</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Pesquisa</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Pós-doc</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://www.gov.br/capes/pt-br/acesso-a-informacao/prestacao-de-contas-e-cobranca-administrativa/auxilio-financeiro-a-projeto-educacional-ou-de-pesquisa-e-pos-graduacao-auxpe</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Manual Cartão Pesquisador</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>CAPES</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Pesquisa</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Pesquisa / Geral</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/documentos/09042024_manual-cartao-pesquisador-capes-2024-v04.pdf</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Termo Uso e Politica de Privacidade App Pesquisador</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>CAPES</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Pesquisa</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Pesquisa / Geral</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://www.gov.br/capes/pt-br/acesso-a-informacao/privacidade-e-protecao-de-dados-pessoais/termo-uso-e-politica-de-privacidade-app-pesquisador</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Bolsas</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Fulbright</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Pesquisa</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Pesquisa / Geral</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://fulbright.org.br/bolsas//bolsas-para-brasileiros</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Fulbright dobra número de bolsas de doutorado sanduíche nos EUA e reajusta valores em até 120%</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Fulbright</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Pesquisa</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Doutorado</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://fulbright.org.br/noticias/fulbright-dobra-numero-de-bolsas-de-doutorado-sanduiche-nos-eua/</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>other selected funding organisations</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>DAAD</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Alemanha</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Pesquisa</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Pesquisa / Geral</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://www.daad.de/en/study-and-research-in-germany/scholarships/scholarship-database/information-on-other-funding-organisations/</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>important scholarship information</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>DAAD</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Alemanha</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Pesquisa</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Pesquisa / Geral</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>https://www.daad.de/en/study-and-research-in-germany/scholarships/important-information-for-scholarship-applicants/</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Horizon Europe – Funding &amp; Tenders Portal</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
           <t>Horizon Europe</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="C52" t="inlineStr">
         <is>
           <t>Europa</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>Pesquisa</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Pesquisa</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
         <is>
           <t>Doutorado/Pós-doc</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="F52" t="inlineStr">
         <is>
           <t>Variável</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="G52" t="inlineStr">
         <is>
           <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>

--- a/bolsas/bolsas_pesquisa.xlsx
+++ b/bolsas/bolsas_pesquisa.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bolsas" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Bolsas'!$A$1:$H$144</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Bolsas'!$A$1:$H$146</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H144"/>
+  <dimension ref="A1:H146"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="70" customWidth="1" min="1" max="1"/>
@@ -6500,8 +6500,92 @@
         </is>
       </c>
     </row>
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>Stanford Cancer Research Education Program (SCREP)</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>NIH Reporter</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>EUA</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+      <c r="E145" s="2" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F145" s="2" t="inlineStr">
+        <is>
+          <t>2031-04-30</t>
+        </is>
+      </c>
+      <c r="G145" s="3" t="inlineStr">
+        <is>
+          <t>https://reporter.nih.gov/project-details/11264575</t>
+        </is>
+      </c>
+      <c r="H145" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>Integrating Behavioral Pain Management to Improve Physical Activity in Family-based Behavioral Treatment for Pediatric Obesity</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>NIH Reporter</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>EUA</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="E146" s="2" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F146" s="2" t="inlineStr">
+        <is>
+          <t>2031-02-28</t>
+        </is>
+      </c>
+      <c r="G146" s="3" t="inlineStr">
+        <is>
+          <t>https://reporter.nih.gov/project-details/11302411</t>
+        </is>
+      </c>
+      <c r="H146" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H144"/>
+  <autoFilter ref="A1:H146"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId2"/>
@@ -6646,6 +6730,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G142" r:id="rId141"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G143" r:id="rId142"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G146" r:id="rId145"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/bolsas/bolsas_pesquisa.xlsx
+++ b/bolsas/bolsas_pesquisa.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bolsas" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Bolsas'!$A$1:$H$146</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Bolsas'!$A$1:$H$159</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H146"/>
+  <dimension ref="A1:H159"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="70" customWidth="1" min="1" max="1"/>
@@ -6584,8 +6584,554 @@
         </is>
       </c>
     </row>
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>MES-CUBA Projetos - MESCUBA-PROJETOS 12/2026</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>CAPES (Bertha)</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
+        <is>
+          <t>Projeto</t>
+        </is>
+      </c>
+      <c r="E147" s="2" t="inlineStr">
+        <is>
+          <t>Doutorado</t>
+        </is>
+      </c>
+      <c r="F147" s="2" t="inlineStr">
+        <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="G147" s="3" t="inlineStr">
+        <is>
+          <t>https://inscricao.capes.gov.br/edital/MESCUBAPROJ2026</t>
+        </is>
+      </c>
+      <c r="H147" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>PROEB - CAMINHOS AMEFRICANOS: PROGRAMA INTERCÂMBIOS SUL-SUL. EDIÇÃO MOÇAMBIQUE - PROEB - CAMINHOS AMEFRICANOS - EDIÇÃO MOÇAMBIQUE 2026</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>CAPES (Bertha)</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
+        <is>
+          <t>Bolsa</t>
+        </is>
+      </c>
+      <c r="E148" s="2" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F148" s="2" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="G148" s="3" t="inlineStr">
+        <is>
+          <t>https://inscricao.capes.gov.br/edital/PROEB-CA-2026</t>
+        </is>
+      </c>
+      <c r="H148" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>Prêmio Fortec de Inovação 2026: inscrições abertas até 10/05</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>CNPq</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
+        <is>
+          <t>Multiplas</t>
+        </is>
+      </c>
+      <c r="E149" s="2" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F149" s="2" t="inlineStr">
+        <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="G149" s="3" t="inlineStr">
+        <is>
+          <t>https://www.gov.br/cnpq/pt-br/assuntos/noticias/oportunidades-externas/fortec-esta-com-inscricoes-abertas-ate-10-05-para-premio-de-inovacao</t>
+        </is>
+      </c>
+      <c r="H149" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>Ciências Exatas e da Terra: Zelinda Leão recebe título de Pesquisadora Emérita do CNPq por pesquisas sobre conservação de corais</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>CNPq</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
+        <is>
+          <t>Multiplas</t>
+        </is>
+      </c>
+      <c r="E150" s="2" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F150" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="G150" s="3" t="inlineStr">
+        <is>
+          <t>https://www.gov.br/cnpq/pt-br/assuntos/noticias/premios/uma-vida-dedicada-ao-estudo-dos-processos-naturais-atuantes-nas-areas-de-recife</t>
+        </is>
+      </c>
+      <c r="H150" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>NexBio Amazônia</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>FAPESP (Chamadas)</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
+        <is>
+          <t>Chamada Publica</t>
+        </is>
+      </c>
+      <c r="E151" s="2" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F151" s="2" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G151" s="3" t="inlineStr">
+        <is>
+          <t>https://fapesp.br/18132</t>
+        </is>
+      </c>
+      <c r="H151" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>Chamada de Propostas FAPESP/CONFAP/ERC 2026</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>FAPESP (Chamadas)</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
+        <is>
+          <t>Chamada Publica</t>
+        </is>
+      </c>
+      <c r="E152" s="2" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F152" s="2" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G152" s="3" t="inlineStr">
+        <is>
+          <t>https://fapesp.br/18135</t>
+        </is>
+      </c>
+      <c r="H152" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t>Chamada de Propostas FAPESP e Fundo para o Desenvolvimento da Ciência e da Tecnologia de Macau (FDCT) 2026</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>FAPESP (Chamadas)</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
+        <is>
+          <t>Chamada Publica</t>
+        </is>
+      </c>
+      <c r="E153" s="2" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F153" s="2" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G153" s="3" t="inlineStr">
+        <is>
+          <t>https://fapesp.br/18167</t>
+        </is>
+      </c>
+      <c r="H153" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>CP 11/26: SEURS - Chamada Pública 11/2026 - Apoio Institucional para Participação na 44º edição do Seminário de Extensão Universitária da Região Sul – SEURS</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>FAPPR / Fundacao Araucaria</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
+        <is>
+          <t>Chamada Publica</t>
+        </is>
+      </c>
+      <c r="E154" s="2" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F154" s="2" t="inlineStr">
+        <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="G154" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fappr.pr.gov.br/sites/fundacao-araucaria/arquivos_restritos/files/documento/2026-05/cp_11-2026_seurs.pdf</t>
+        </is>
+      </c>
+      <c r="H154" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
+        <is>
+          <t>CP 10/26: Pró PET ( Pesquisa-Ensino-Extensão) - Chamada Pública 10/2026 - Programa de Apoio à Educação Tutorial Pesquisa-Ensino-Extensão (Pró PET)</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>FAPPR / Fundacao Araucaria</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
+        <is>
+          <t>Chamada Publica</t>
+        </is>
+      </c>
+      <c r="E155" s="2" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F155" s="2" t="inlineStr">
+        <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="G155" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fappr.pr.gov.br/sites/fundacao-araucaria/arquivos_restritos/files/documento/2026-04/cp_10-2026_propet.pdf</t>
+        </is>
+      </c>
+      <c r="H155" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>Battery Innovation Programme: battery skills initiatives</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>UKRI</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>Reino Unido</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
+        <is>
+          <t>Multiplas</t>
+        </is>
+      </c>
+      <c r="E156" s="2" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F156" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 07 Ma</t>
+        </is>
+      </c>
+      <c r="G156" s="3" t="inlineStr">
+        <is>
+          <t>https://www.ukri.org/opportunity/battery-innovation-programme-battery-skills-initiatives/</t>
+        </is>
+      </c>
+      <c r="H156" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
+        <is>
+          <t>National Materials Innovation Programme: Feasibility studies Round 2</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>UKRI</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>Reino Unido</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
+        <is>
+          <t>Multiplas</t>
+        </is>
+      </c>
+      <c r="E157" s="2" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F157" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 05 Ma</t>
+        </is>
+      </c>
+      <c r="G157" s="3" t="inlineStr">
+        <is>
+          <t>https://www.ukri.org/opportunity/national-materials-innovation-programme-feasibility-studies-round-2/</t>
+        </is>
+      </c>
+      <c r="H157" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>Particle Physics Experiment Consolidated Grants 2026</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>UKRI</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>Reino Unido</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
+        <is>
+          <t>Multiplas</t>
+        </is>
+      </c>
+      <c r="E158" s="2" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F158" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 01 Ma</t>
+        </is>
+      </c>
+      <c r="G158" s="3" t="inlineStr">
+        <is>
+          <t>https://www.ukri.org/opportunity/particle-physics-experiment-consolidated-grants-2026/</t>
+        </is>
+      </c>
+      <c r="H158" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>2026 Nasopharyngeal Carcinoma Gordon Research Conference</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>NIH Reporter</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>EUA</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+      <c r="E159" s="2" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F159" s="2" t="inlineStr">
+        <is>
+          <t>2027-04-30</t>
+        </is>
+      </c>
+      <c r="G159" s="3" t="inlineStr">
+        <is>
+          <t>https://reporter.nih.gov/project-details/11319955</t>
+        </is>
+      </c>
+      <c r="H159" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H146"/>
+  <autoFilter ref="A1:H159"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId2"/>
@@ -6732,6 +7278,19 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G144" r:id="rId143"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G145" r:id="rId144"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G159" r:id="rId158"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
